--- a/tables/hybrid_fem_dijkstra_dem_tables.xlsx
+++ b/tables/hybrid_fem_dijkstra_dem_tables.xlsx
@@ -15350,7 +15350,7 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>dijkstra_warning_time_h</t>
+          <t>dijkstra_screening_crossing_time_h</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
